--- a/docs/almica-contenido-PARA-MARIANA-20260924.xlsx
+++ b/docs/almica-contenido-PARA-MARIANA-20260924.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -175,6 +175,12 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00263B33"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -278,7 +284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -437,6 +443,10 @@
     <xf numFmtId="0" fontId="26" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -450,6 +460,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -604,7 +617,7 @@
     </comment>
     <comment ref="N3" authorId="1" shapeId="0">
       <text>
-        <t>Opcional. Vacío = se usa la foto de la tarjeta. Ver «Pendientes», punto 7.</t>
+        <t>Opcional y verificado contra Figma: el diseño reutiliza la foto de la tarjeta. Déjalo vacío.</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
@@ -615,7 +628,7 @@
     </comment>
     <comment ref="N4" authorId="1" shapeId="0">
       <text>
-        <t>Opcional. Vacío = se usa la foto de la tarjeta. Ver «Pendientes», punto 7.</t>
+        <t>Opcional y verificado contra Figma: el diseño reutiliza la foto de la tarjeta. Déjalo vacío.</t>
       </text>
     </comment>
     <comment ref="M5" authorId="0" shapeId="0">
@@ -626,7 +639,7 @@
     </comment>
     <comment ref="N5" authorId="1" shapeId="0">
       <text>
-        <t>Opcional. Vacío = se usa la foto de la tarjeta. Ver «Pendientes», punto 7.</t>
+        <t>Opcional y verificado contra Figma: el diseño reutiliza la foto de la tarjeta. Déjalo vacío.</t>
       </text>
     </comment>
     <comment ref="M6" authorId="0" shapeId="0">
@@ -637,7 +650,7 @@
     </comment>
     <comment ref="N6" authorId="1" shapeId="0">
       <text>
-        <t>Opcional. Vacío = se usa la foto de la tarjeta. Ver «Pendientes», punto 7.</t>
+        <t>Opcional y verificado contra Figma: el diseño reutiliza la foto de la tarjeta. Déjalo vacío.</t>
       </text>
     </comment>
     <comment ref="B7" authorId="0" shapeId="0">
@@ -653,7 +666,7 @@
     </comment>
     <comment ref="N7" authorId="1" shapeId="0">
       <text>
-        <t>Opcional. Vacío = se usa la foto de la tarjeta. Ver «Pendientes», punto 7.</t>
+        <t>Opcional y verificado contra Figma: el diseño reutiliza la foto de la tarjeta. Déjalo vacío.</t>
       </text>
     </comment>
     <comment ref="M8" authorId="0" shapeId="0">
@@ -664,7 +677,7 @@
     </comment>
     <comment ref="N8" authorId="1" shapeId="0">
       <text>
-        <t>Opcional. Vacío = se usa la foto de la tarjeta. Ver «Pendientes», punto 7.</t>
+        <t>Opcional y verificado contra Figma: el diseño reutiliza la foto de la tarjeta. Déjalo vacío.</t>
       </text>
     </comment>
     <comment ref="M9" authorId="0" shapeId="0">
@@ -675,7 +688,7 @@
     </comment>
     <comment ref="N9" authorId="1" shapeId="0">
       <text>
-        <t>Opcional. Vacío = se usa la foto de la tarjeta. Ver «Pendientes», punto 7.</t>
+        <t>Opcional y verificado contra Figma: el diseño reutiliza la foto de la tarjeta. Déjalo vacío.</t>
       </text>
     </comment>
     <comment ref="M10" authorId="0" shapeId="0">
@@ -685,7 +698,7 @@
     </comment>
     <comment ref="N10" authorId="1" shapeId="0">
       <text>
-        <t>Opcional. Vacío = se usa la foto de la tarjeta. Ver «Pendientes», punto 7.</t>
+        <t>Opcional y verificado contra Figma: el diseño reutiliza la foto de la tarjeta. Déjalo vacío.</t>
       </text>
     </comment>
     <comment ref="B11" authorId="0" shapeId="0">
@@ -700,7 +713,7 @@
     </comment>
     <comment ref="N11" authorId="1" shapeId="0">
       <text>
-        <t>Opcional. Vacío = se usa la foto de la tarjeta. Ver «Pendientes», punto 7.</t>
+        <t>Opcional y verificado contra Figma: el diseño reutiliza la foto de la tarjeta. Déjalo vacío.</t>
       </text>
     </comment>
     <comment ref="B12" authorId="0" shapeId="0">
@@ -715,7 +728,7 @@
     </comment>
     <comment ref="N12" authorId="1" shapeId="0">
       <text>
-        <t>Opcional. Vacío = se usa la foto de la tarjeta. Ver «Pendientes», punto 7.</t>
+        <t>Opcional y verificado contra Figma: el diseño reutiliza la foto de la tarjeta. Déjalo vacío.</t>
       </text>
     </comment>
     <comment ref="B13" authorId="0" shapeId="0">
@@ -730,7 +743,7 @@
     </comment>
     <comment ref="N13" authorId="1" shapeId="0">
       <text>
-        <t>Opcional. Vacío = se usa la foto de la tarjeta. Ver «Pendientes», punto 7.</t>
+        <t>Opcional y verificado contra Figma: el diseño reutiliza la foto de la tarjeta. Déjalo vacío.</t>
       </text>
     </comment>
   </commentList>
@@ -745,7 +758,6 @@
     <author>tc={c36060fb-bf10-42c5-99d5-612a568c639a}</author>
     <author>tc={1b86ba56-ba6d-4dcf-afb2-ce61f74cdaa5}</author>
     <author>tc={56819111-a68e-40d5-b929-18ebfc100f00}</author>
-    <author>Pendientes</author>
   </authors>
   <commentList>
     <comment ref="C21" authorId="0" shapeId="0">
@@ -793,21 +805,6 @@
 </t>
       </text>
     </comment>
-    <comment ref="E31" authorId="5" shapeId="0">
-      <text>
-        <t>Confirmar si se queda vacío. Ver «Pendientes», punto 3.</t>
-      </text>
-    </comment>
-    <comment ref="E32" authorId="5" shapeId="0">
-      <text>
-        <t>Confirmar si se queda vacío. Ver «Pendientes», punto 3.</t>
-      </text>
-    </comment>
-    <comment ref="E33" authorId="5" shapeId="0">
-      <text>
-        <t>Confirmar si se queda vacío. Ver «Pendientes», punto 3.</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -816,8 +813,8 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>None</author>
+    <author>tc={ce6abbf4-4734-4531-a36f-947aca8a665e}</author>
     <author>Pendientes</author>
-    <author>tc={ce6abbf4-4734-4531-a36f-947aca8a665e}</author>
   </authors>
   <commentList>
     <comment ref="B3" authorId="0" shapeId="0">
@@ -826,22 +823,12 @@
 En el bloque de Inicio tu hoja usa otro resumen: «Un viaje de profundización en la percepción energética y el lenguaje sutil del cuerpo.» Se usó el del listado de Cursos.</t>
       </text>
     </comment>
-    <comment ref="G3" authorId="1" shapeId="0">
-      <text>
-        <t>Decisión: un solo resumen por curso. Ver «Pendientes», punto 2.</t>
-      </text>
-    </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
         <t>En el bloque de Inicio tu hoja usa otro resumen para este curso: «Herramientas para acceder a estados expandidos de consciencia y trabajar desde ahí.» El modelo tiene un solo campo; se usó el del listado de Cursos. Dime si prefieres el otro.</t>
       </text>
     </comment>
-    <comment ref="G4" authorId="1" shapeId="0">
-      <text>
-        <t>Decisión: un solo resumen por curso. Ver «Pendientes», punto 2.</t>
-      </text>
-    </comment>
-    <comment ref="D5" authorId="2" shapeId="0">
+    <comment ref="D5" authorId="1" shapeId="0">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -857,9 +844,9 @@
 2) La etiqueta dice «Curso básico de canalización» pero el nivel es «Abierto a todos» (pregunta abierta Q9). Sigue sin resolverse.</t>
       </text>
     </comment>
-    <comment ref="G5" authorId="1" shapeId="0">
+    <comment ref="F5" authorId="2" shapeId="0">
       <text>
-        <t>Decisión: un solo resumen por curso. Ver «Pendientes», punto 2.</t>
+        <t>Reescribir: hoy repite el tagline. Ver «Pendientes», punto 1.</t>
       </text>
     </comment>
   </commentList>
@@ -874,17 +861,12 @@
   <commentList>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
-        <t>Falta: WhatsApp. Ver «Pendientes», punto 4.</t>
-      </text>
-    </comment>
-    <comment ref="B8" authorId="0" shapeId="0">
-      <text>
-        <t>Falta: enlace de la red social. Ver «Pendientes», punto 1.</t>
+        <t>Falta: WhatsApp. Ver «Pendientes», punto 2.</t>
       </text>
     </comment>
     <comment ref="B9" authorId="0" shapeId="0">
       <text>
-        <t>Falta: enlace de la red social. Ver «Pendientes», punto 1.</t>
+        <t>La marca no usa TikTok (confirmado). Se dejó vacío y el icono está comentado en el tema. Si abren cuenta, pega aquí la URL y descomenta social_tiktok en template-parts/footer/social.php.</t>
       </text>
     </comment>
   </commentList>
@@ -2645,7 +2627,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="B5" s="57" t="n"/>
+      <c r="B5" s="59" t="n"/>
       <c r="C5" s="41" t="inlineStr">
         <is>
           <t>Número o enlace de WhatsApp. Vacío oculta las menciones a WhatsApp.</t>
@@ -2692,7 +2674,11 @@
           <t>social_facebook</t>
         </is>
       </c>
-      <c r="B8" s="57" t="n"/>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100063472513452</t>
+        </is>
+      </c>
       <c r="C8" s="41" t="inlineStr">
         <is>
           <t>URL completa. Vacío oculta el botón.</t>
@@ -2705,7 +2691,7 @@
           <t>social_tiktok</t>
         </is>
       </c>
-      <c r="B9" s="57" t="n"/>
+      <c r="B9" s="36" t="n"/>
       <c r="C9" s="41" t="inlineStr">
         <is>
           <t>URL completa. Vacío oculta el botón.</t>
@@ -5624,7 +5610,7 @@
       <c r="C2" s="4" t="n"/>
     </row>
     <row r="3" ht="60" customHeight="1" s="50">
-      <c r="A3" s="58" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>LISTO</t>
         </is>
@@ -5636,7 +5622,7 @@
       </c>
       <c r="C3" s="36" t="inlineStr">
         <is>
-          <t>Tu hoja pone a «Alberto Solís» como facilitador de ese curso. En todo lo demás —Figma, los otros dos cursos, Acerca de— sólo aparece Alma Solís. ¿Es un error de dedo o es otra persona? Lo dejé en alma-solis; si es otra persona hay que darla de alta con su rol, biografía y foto. Sí es otra persona, ya solicité a la diseñadora esos cambios. — RESUELTO: ya tiene ficha propia en «profesionales» y el curso lo usa.</t>
+          <t>Tu hoja pone a «Alberto Solís» como facilitador de ese curso. En todo lo demás —Figma, los otros dos cursos, Acerca de— sólo aparece Alma Solís. ¿Es un error de dedo o es otra persona? Lo dejé en alma-solis; si es otra persona hay que darla de alta con su rol, biografía y foto. Sí es otra persona, ya solicité a la diseñadora esos cambios. — RESUELTO: ya tiene ficha propia y el curso lo usa.</t>
         </is>
       </c>
     </row>
@@ -5675,9 +5661,9 @@
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" s="50">
-      <c r="A6" s="59" t="inlineStr">
-        <is>
-          <t>DECIDIR</t>
+      <c r="A6" s="61" t="inlineStr">
+        <is>
+          <t>FALTA</t>
         </is>
       </c>
       <c r="B6" s="45" t="inlineStr">
@@ -5687,7 +5673,7 @@
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>Hay dos textos cortos distintos por curso: uno en el bloque de Inicio y otro en el listado de Cursos. El modelo tiene UN solo campo (summary). Usé el del listado. Si quieres el de Inicio, está anotado en el comentario de cada celda. Perdón esto no te entiendo, lo vemos mañana en la mañana — SIGUE ABIERTO. Ver «Pendientes», punto 2.</t>
+          <t>Hay dos textos cortos distintos por curso: uno en el bloque de Inicio y otro en el listado de Cursos. El modelo tiene UN solo campo (summary). Usé el del listado. Si quieres el de Inicio, está anotado en el comentario de cada celda. Perdón esto no te entiendo, lo vemos mañana en la mañana — Clantanra y Riutunmi ya se arreglaron. Falta sólo «Lo Que Nadie Nos Enseñó»: ver «Pendientes», punto 1.</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5729,7 @@
       </c>
     </row>
     <row r="10" ht="60" customHeight="1" s="50">
-      <c r="A10" s="58" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>LISTO</t>
         </is>
@@ -5755,12 +5741,12 @@
       </c>
       <c r="C10" s="36" t="inlineStr">
         <is>
-          <t>Sigue sin resolverse: la etiqueta dice «Curso básico de canalización» pero el nivel es «Abierto a todos» (pregunta abierta Q9). — RESUELTO: nivel «abierto» y etiqueta coinciden.</t>
+          <t>Sigue sin resolverse: la etiqueta dice «Curso básico de canalización» pero el nivel es «Abierto a todos» (pregunta abierta Q9). — RESUELTO: nivel «abierto», coincide con la etiqueta.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1" s="50">
-      <c r="A11" s="60" t="inlineStr">
+      <c r="A11" s="62" t="inlineStr">
         <is>
           <t>LISTO</t>
         </is>
@@ -5772,7 +5758,7 @@
       </c>
       <c r="C11" s="36" t="inlineStr">
         <is>
-          <t>Limpieza Energética de Lugares · Escaneo y Balance Energético · Conexión con Seres Trascendidos · Conexión con Registros · Futuros Posibles · Limpieza y Conexión con Personas · Limpieza y Conexión Emocional con Personas. Falta descripción y beneficios en los 7, y resumen en 5 de ellos. Creo que ya quedó — RESUELTO: los 11 servicios ya tienen resumen, descripción y beneficios.</t>
+          <t>Limpieza Energética de Lugares · Escaneo y Balance Energético · Conexión con Seres Trascendidos · Conexión con Registros · Futuros Posibles · Limpieza y Conexión con Personas · Limpieza y Conexión Emocional con Personas. Falta descripción y beneficios en los 7, y resumen en 5 de ellos. Creo que ya quedó — RESUELTO: los 11 servicios están completos.</t>
         </is>
       </c>
     </row>
@@ -5794,45 +5780,45 @@
       </c>
     </row>
     <row r="13" ht="60" customHeight="1" s="50">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="63" t="inlineStr">
+        <is>
+          <t>FALTA</t>
+        </is>
+      </c>
+      <c r="B13" s="45" t="inlineStr">
+        <is>
+          <t>Fotos de terapeutas</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>Faltan las de Elizabeth, Gabriela y Tonathiu. Cuadradas, mínimo 400×400 px. — RECIBIDAS, pero a 200×200 px. Ver «Pendientes», punto 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1" s="50">
+      <c r="A14" s="62" t="inlineStr">
         <is>
           <t>LISTO</t>
         </is>
       </c>
-      <c r="B13" s="45" t="inlineStr">
-        <is>
-          <t>Fotos de terapeutas</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="inlineStr">
-        <is>
-          <t>Faltan las de Elizabeth, Gabriela y Tonathiu. Cuadradas, mínimo 400×400 px. — RECIBIDAS, pero a 200×200 px. Ver «Pendientes», punto 6.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1" s="50">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="B14" s="45" t="inlineStr">
+        <is>
+          <t>Carpetas de imágenes de 4 servicios</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>Conexión con Registros, Futuros Posibles, Limpieza y Conexión con Personas y Limpieza y Conexión Emocional no traen enlace de Drive. — RESUELTO: las 11 tarjetas tienen foto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1" s="50">
+      <c r="A15" s="62" t="inlineStr">
         <is>
           <t>LISTO</t>
         </is>
       </c>
-      <c r="B14" s="45" t="inlineStr">
-        <is>
-          <t>Carpetas de imágenes de 4 servicios</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="inlineStr">
-        <is>
-          <t>Conexión con Registros, Futuros Posibles, Limpieza y Conexión con Personas y Limpieza y Conexión Emocional no traen enlace de Drive. — RESUELTO: las 11 tarjetas tienen foto y la cabecera la reutiliza.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1" s="50">
-      <c r="A15" s="60" t="inlineStr">
-        <is>
-          <t>LISTO</t>
-        </is>
-      </c>
       <c r="B15" s="45" t="inlineStr">
         <is>
           <t>Textos legales</t>
@@ -5840,12 +5826,12 @@
       </c>
       <c r="C15" s="36" t="inlineStr">
         <is>
-          <t>Términos y condiciones y Aviso de privacidad están vacíos en tu hoja. La plantilla ya está hecha; sólo falta el texto, que debe venir del cliente o de su abogado. — RESUELTO: Aviso de Privacidad y Términos ya están publicados en el sitio.</t>
+          <t>Términos y condiciones y Aviso de privacidad están vacíos en tu hoja. La plantilla ya está hecha; sólo falta el texto, que debe venir del cliente o de su abogado. — RESUELTO: ambos documentos ya están publicados.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1" s="50">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="62" t="inlineStr">
         <is>
           <t>LISTO</t>
         </is>
@@ -6986,16 +6972,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" style="50" min="1" max="1"/>
     <col width="11" customWidth="1" style="50" min="2" max="2"/>
-    <col width="20" customWidth="1" style="50" min="3" max="3"/>
-    <col width="12" customWidth="1" style="50" min="4" max="4"/>
-    <col width="52" customWidth="1" style="50" min="5" max="5"/>
-    <col width="40" customWidth="1" style="50" min="6" max="6"/>
-    <col width="52" customWidth="1" style="50" min="7" max="7"/>
+    <col width="16" customWidth="1" style="50" min="3" max="3"/>
+    <col width="26" customWidth="1" style="50" min="4" max="4"/>
+    <col width="54" customWidth="1" style="50" min="5" max="5"/>
+    <col width="38" customWidth="1" style="50" min="6" max="6"/>
+    <col width="50" customWidth="1" style="50" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7035,7 +7021,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="66" customHeight="1" s="50">
+    <row r="2" ht="92" customHeight="1" s="50">
       <c r="A2" s="53" t="n">
         <v>1</v>
       </c>
@@ -7046,66 +7032,66 @@
       </c>
       <c r="C2" s="53" t="inlineStr">
         <is>
-          <t>ajustes</t>
+          <t>cursos</t>
         </is>
       </c>
       <c r="D2" s="53" t="inlineStr">
         <is>
-          <t>8 y 9 · columna value</t>
+          <t>fila 5 · columna summary</t>
         </is>
       </c>
       <c r="E2" s="53" t="inlineStr">
         <is>
-          <t>Faltan los enlaces de Facebook y de TikTok.</t>
+          <t>El resumen de «Lo Que Nadie Nos Enseñó» repite casi palabra por palabra su propio tagline (coinciden en un 94%), así que la ficha dice lo mismo dos veces seguidas. Clantanra y Riutunmi ya se arreglaron usando el texto del bloque de Inicio; este curso no tenía segunda versión.</t>
         </is>
       </c>
       <c r="F2" s="53" t="inlineStr">
         <is>
-          <t>Los iconos del pie de página, en todas las páginas.</t>
+          <t>La tarjeta del curso en Inicio y en Cursos, y el encabezado de su propia página, uno debajo del otro.</t>
         </is>
       </c>
       <c r="G2" s="53" t="inlineStr">
         <is>
-          <t>La URL completa, con el mismo formato que Instagram (fila 7). Si la marca no tiene esa red, escribe: no aplica</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="66" customHeight="1" s="50">
+          <t>Un texto corto y DISTINTO del tagline, máximo 160 caracteres. El tagline actual es: «Herramientas prácticas para afrontar los desafíos cotidianos con mayor conciencia y equilibrio.»</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="92" customHeight="1" s="50">
       <c r="A3" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="54" t="inlineStr">
-        <is>
-          <t>Alta</t>
+      <c r="B3" s="55" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="C3" s="53" t="inlineStr">
         <is>
-          <t>cursos</t>
+          <t>ajustes</t>
         </is>
       </c>
       <c r="D3" s="53" t="inlineStr">
         <is>
-          <t>3, 4 y 5 · columna summary</t>
+          <t>fila 5 · columna value</t>
         </is>
       </c>
       <c r="E3" s="53" t="inlineStr">
         <is>
-          <t>DECISIÓN: hay dos textos cortos por curso (uno para Inicio y otro para el listado de Cursos) pero el sitio sólo tiene un campo. Ahora está cargado el del listado; el de Inicio quedó guardado en el comentario de la celda.</t>
+          <t>Falta el número de WhatsApp. Quedó sin definir.</t>
         </is>
       </c>
       <c r="F3" s="53" t="inlineStr">
         <is>
-          <t>La tarjeta del curso, que aparece igual en Inicio y en Cursos.</t>
+          <t>El botón de contacto.</t>
         </is>
       </c>
       <c r="G3" s="53" t="inlineStr">
         <is>
-          <t>Elige UN solo texto por curso y déjalo en summary. Recomendado: máximo 160 caracteres.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="66" customHeight="1" s="50">
+          <t>Formato +52 55 1234 5678. Si se usa el mismo que ya está en «phone», cópialo. Si no se va a usar, escribe: no aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="92" customHeight="1" s="50">
       <c r="A4" s="53" t="n">
         <v>3</v>
       </c>
@@ -7116,180 +7102,125 @@
       </c>
       <c r="C4" s="53" t="inlineStr">
         <is>
-          <t>servicio_beneficios</t>
+          <t>(fotos, no es una pestaña)</t>
         </is>
       </c>
       <c r="D4" s="53" t="inlineStr">
         <is>
-          <t>31, 32 y 33 · columna description</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E4" s="53" t="inlineStr">
         <is>
-          <t>Estos 3 beneficios de «Limpieza y Conexión Emocional con Personas» sólo tienen la mitad verde (title) y no la crema (description). Los otros 28 beneficios del sitio sí tienen las dos.</t>
+          <t>Las 5 fotos de terapeutas miden 200×200 px y lo acordado era un mínimo de 400×400. Se ven suaves en pantallas retina. Alma es la única con foto en alta resolución.</t>
         </is>
       </c>
       <c r="F4" s="53" t="inlineStr">
         <is>
-          <t>Las tarjetas de «Lo que esta sesión puede ofrecerte».</t>
+          <t>El círculo con la foto en «Quién imparte» y en Acerca de.</t>
         </is>
       </c>
       <c r="G4" s="53" t="inlineStr">
         <is>
-          <t>Confirma si se quedan así a propósito, o escribe la segunda línea en minúscula, como si continuara la frase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="66" customHeight="1" s="50">
-      <c r="A5" s="53" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="55" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C5" s="53" t="inlineStr">
-        <is>
-          <t>ajustes</t>
-        </is>
-      </c>
-      <c r="D5" s="53" t="inlineStr">
-        <is>
-          <t>5 · columna value</t>
-        </is>
-      </c>
-      <c r="E5" s="53" t="inlineStr">
-        <is>
-          <t>Falta el número de WhatsApp.</t>
-        </is>
-      </c>
-      <c r="F5" s="53" t="inlineStr">
-        <is>
-          <t>El botón de contacto.</t>
-        </is>
-      </c>
-      <c r="G5" s="53" t="inlineStr">
-        <is>
-          <t>Formato +52 55 1234 5678. Si no se va a usar, escribe: no aplica</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="66" customHeight="1" s="50">
-      <c r="A6" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="55" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C6" s="53" t="inlineStr">
-        <is>
-          <t>(fotos, no es una pestaña)</t>
-        </is>
-      </c>
-      <c r="D6" s="53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="53" t="inlineStr">
-        <is>
-          <t>Las 5 fotos nuevas de terapeutas miden 200×200 px y lo acordado era mínimo 400×400. Alma es la única con foto en alta resolución.</t>
-        </is>
-      </c>
-      <c r="F6" s="53" t="inlineStr">
-        <is>
-          <t>El círculo con la foto en «Quién imparte» y en Acerca de.</t>
-        </is>
-      </c>
-      <c r="G6" s="53" t="inlineStr">
-        <is>
           <t>Pedir al cliente los archivos originales, cuadrados, mínimo 400×400 px (mejor 800×800).</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="66" customHeight="1" s="50">
-      <c r="A7" s="53" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="55" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="C7" s="53" t="inlineStr">
-        <is>
-          <t>cursos</t>
-        </is>
-      </c>
-      <c r="D7" s="53" t="inlineStr">
-        <is>
-          <t>3 · columnas price y duration</t>
-        </is>
-      </c>
-      <c r="E7" s="53" t="inlineStr">
-        <is>
-          <t>Clantanra no trae precio ni duración. Entiendo que es a propósito («precio a consultar»).</t>
-        </is>
-      </c>
-      <c r="F7" s="53" t="inlineStr">
-        <is>
-          <t>La tarjeta de Inversión, que se oculta entera si no hay precio.</t>
-        </is>
-      </c>
-      <c r="G7" s="53" t="inlineStr">
-        <is>
-          <t>Sólo confirma que es correcto. Si sí hay precio, escríbelo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="66" customHeight="1" s="50">
-      <c r="A8" s="53" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="55" t="inlineStr">
-        <is>
-          <t>Opcional</t>
-        </is>
-      </c>
-      <c r="C8" s="53" t="inlineStr">
-        <is>
-          <t>servicios</t>
-        </is>
-      </c>
-      <c r="D8" s="53" t="inlineStr">
-        <is>
-          <t>3 a 13 · columna hero_image</t>
-        </is>
-      </c>
-      <c r="E8" s="53" t="inlineStr">
-        <is>
-          <t>NO es un hueco: esta columna sólo sirve para poner una foto DISTINTA en la cabecera. Vacía —como está hoy— el sitio reutiliza la foto de la tarjeta, y así se ve ya publicado. No hay nada roto.</t>
-        </is>
-      </c>
-      <c r="F8" s="53" t="inlineStr">
-        <is>
-          <t>La franja grande al abrir un servicio. Hoy muestra la foto de la tarjeta a todo lo ancho, con un velo oscuro encima.</t>
-        </is>
-      </c>
-      <c r="G8" s="53" t="inlineStr">
-        <is>
-          <t>Déjala vacía si la foto de la tarjeta funciona. Llénala sólo si el cliente quiere otra imagen: nombre de archivo, horizontal, mínimo 1600×900 px.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="62" customHeight="1" s="50">
-      <c r="A10" s="56" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="56" t="inlineStr">
+        <is>
+          <t>Ya resuelto — no hace falta hacer nada aquí</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" s="50">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B7" s="57" t="inlineStr">
+        <is>
+          <t>Facebook y TikTok: Facebook ya quedó cargado. La marca no usa TikTok, así que el icono se quitó del pie de página.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="50">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B8" s="57" t="inlineStr">
+        <is>
+          <t>Resúmenes de Clantanra y Riutunmi: se cambiaron por los textos del bloque de Inicio, que no repiten el tagline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="50">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B9" s="57" t="inlineStr">
+        <is>
+          <t>Los 3 beneficios de «Limpieza y Conexión Emocional»: se revisaron contra Figma y van en un solo color, sin segunda línea. Quedan así.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="50">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B10" s="57" t="inlineStr">
+        <is>
+          <t>Clantanra sin precio ni duración: confirmado, es «precio a consultar».</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" s="50">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B11" s="57" t="inlineStr">
+        <is>
+          <t>hero_image de los 11 servicios: revisado contra Figma. El diseño usa la misma foto de la tarjeta, así que la columna se queda vacía a propósito y no hay nada que conseguir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="50">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B12" s="57" t="inlineStr">
+        <is>
+          <t>Textos legales: Aviso de Privacidad y Términos ya están publicados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="62" customHeight="1" s="50">
+      <c r="A14" s="58" t="inlineStr">
         <is>
           <t>IMPORTANTE al devolver el archivo: no borres ni renombres la fila 1 (los encabezados) ni la columna «slug». En la versión anterior se borró el encabezado «slug» de la pestaña servicios y el sitio no pudo cargar nada hasta repararlo. Puedes añadir filas al final de cualquier pestaña, pero no reordenes ni elimines columnas.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A10:G10"/>
+  <mergeCells count="7">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B11:G11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12579,7 +12510,7 @@
 de dinámicas presentes en tus vínculos.</t>
         </is>
       </c>
-      <c r="E31" s="57" t="n"/>
+      <c r="E31" s="36" t="n"/>
     </row>
     <row r="32" ht="60" customHeight="1" s="50">
       <c r="A32" s="29" t="inlineStr">
@@ -12601,7 +12532,7 @@
 una perspectiva de bienestar integral.</t>
         </is>
       </c>
-      <c r="E32" s="57" t="n"/>
+      <c r="E32" s="36" t="n"/>
     </row>
     <row r="33" ht="60" customHeight="1" s="50">
       <c r="A33" s="29" t="inlineStr">
@@ -12623,7 +12554,7 @@
 de mayor claridad emocional.</t>
         </is>
       </c>
-      <c r="E33" s="57" t="n"/>
+      <c r="E33" s="36" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="50"/>
     <row r="35" ht="15.75" customHeight="1" s="50"/>
@@ -13806,10 +13737,10 @@
       </c>
       <c r="F3" s="36" t="inlineStr">
         <is>
-          <t>Un programa enfocado en el desarrollo del autoconocimiento profundo y la conexión con el propósito personal.</t>
-        </is>
-      </c>
-      <c r="G3" s="57" t="inlineStr">
+          <t>Un viaje de profundización en la percepción energética y el lenguaje sutil del cuerpo.</t>
+        </is>
+      </c>
+      <c r="G3" s="36" t="inlineStr">
         <is>
           <t>Un programa de alta conexión interior para quienes buscan ampliar su percepción e intuición.</t>
         </is>
@@ -13869,10 +13800,10 @@
       </c>
       <c r="F4" s="36" t="inlineStr">
         <is>
-          <t>Un espacio de formación enfocado en el desarrollo de la conciencia y la conexión con dimensiones más profundas del ser.</t>
-        </is>
-      </c>
-      <c r="G4" s="57" t="inlineStr">
+          <t>Herramientas para acceder a estados expandidos de consciencia y trabajar desde ahí.</t>
+        </is>
+      </c>
+      <c r="G4" s="36" t="inlineStr">
         <is>
           <t>Un espacio de formación para el desarrollo de la conciencia y la conexión con dimensiones más profundas del ser.</t>
         </is>
@@ -13936,12 +13867,12 @@
           <t>Curso de canalización abierto a todo público</t>
         </is>
       </c>
-      <c r="F5" s="36" t="inlineStr">
+      <c r="F5" s="59" t="inlineStr">
         <is>
           <t>Un curso con herramientas prácticas para afrontar los desafíos cotidianos con mayor conciencia y equilibrio.</t>
         </is>
       </c>
-      <c r="G5" s="57" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>Herramientas prácticas para afrontar los desafíos cotidianos con mayor conciencia y equilibrio.</t>
         </is>

--- a/docs/almica-contenido-PARA-MARIANA-20260924.xlsx
+++ b/docs/almica-contenido-PARA-MARIANA-20260924.xlsx
@@ -7134,7 +7134,7 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="50">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -7146,7 +7146,7 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="50">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -7158,7 +7158,7 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" s="50">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -7170,7 +7170,7 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="50">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -7182,7 +7182,7 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="50">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -7194,7 +7194,7 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" s="50">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>acerca-de-fundadora.jpg</t>
+          <t>alma-solis.jpg</t>
         </is>
       </c>
       <c r="F3" s="29" t="n">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>elizabeth-de-las-casas.png</t>
+          <t>elizabeth-de-las-casas.jpg</t>
         </is>
       </c>
       <c r="F4" s="29" t="n">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>gabriela-dominguez.png</t>
+          <t>gabriela-dominguez.jpg</t>
         </is>
       </c>
       <c r="F5" s="29" t="n">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>tonathiu-munoz.png</t>
+          <t>tonathiu-munoz.jpg</t>
         </is>
       </c>
       <c r="F6" s="29" t="n">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>perla-barrones.png</t>
+          <t>perla-barrones.jpg</t>
         </is>
       </c>
       <c r="F7" s="29" t="n">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>alberto-solis.png</t>
+          <t>alberto-solis.jpg</t>
         </is>
       </c>
       <c r="F8" s="26" t="n">

--- a/docs/almica-contenido-PARA-MARIANA-20260924.xlsx
+++ b/docs/almica-contenido-PARA-MARIANA-20260924.xlsx
@@ -1131,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E47"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3" customWidth="1" style="50" min="1" max="1"/>
@@ -1141,6 +1141,7 @@
     <col width="8.710000000000001" customWidth="1" style="50" min="6" max="26"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1162,6 +1163,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -1204,6 +1206,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="7" t="inlineStr">
         <is>
@@ -1247,6 +1250,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="30" customHeight="1" s="50">
       <c r="C18" s="15" t="inlineStr">
         <is>
@@ -1254,6 +1258,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="B20" s="7" t="inlineStr">
         <is>
@@ -1317,7 +1322,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Separa los slugs con una barra vertical, sin espacios: gabriela-dominguez|tonathiu-munoz</t>
+          <t>Separa los slugs con una barra vertical, sin espacios: gabriela-dominguez|tonatiuh-munoz</t>
         </is>
       </c>
     </row>
@@ -1368,14 +1373,14 @@
     <row r="31" ht="43.5" customHeight="1" s="50">
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Con tu hoja quedaron cubiertos 4 de los 11 servicios, los 3 cursos, Gabriela Domínguez y todos los textos de página. Lo urgente ahora son los 7 servicios que siguen sin página: hace falta descripción y beneficios en los 7, y el resumen corto en 5 de ellos. Después, el rol y la biografía de Tonathiu Muñoz, que imparte cinco de esos siete.</t>
+          <t>Con tu hoja quedaron cubiertos 4 de los 11 servicios, los 3 cursos, Gabriela Domínguez y todos los textos de página. Lo urgente ahora son los 7 servicios que siguen sin página: hace falta descripción y beneficios en los 7, y el resumen corto en 5 de ellos. Después, el rol y la biografía de Tonatiuh Muñoz, que imparte cinco de esos siete.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="43.5" customHeight="1" s="50">
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Aparte del texto hacen falta FOTOS: las de Elizabeth, Gabriela y Tonathiu (cuadradas, mín. 400×400 px). Y si existen, los enlaces de Instagram, Facebook, TikTok y WhatsApp en la pestaña «ajustes» — son opcionales, pero mientras estén vacíos esos botones no aparecen en la web.</t>
+          <t>Aparte del texto hacen falta FOTOS: las de Elizabeth, Gabriela y Tonatiuh (cuadradas, mín. 400×400 px). Y si existen, los enlaces de Instagram, Facebook, TikTok y WhatsApp en la pestaña «ajustes» — son opcionales, pero mientras estén vacíos esos botones no aparecen en la web.</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5775,7 @@
       </c>
       <c r="B12" s="45" t="inlineStr">
         <is>
-          <t>Tonathiu Muñoz</t>
+          <t>Tonatiuh Muñoz</t>
         </is>
       </c>
       <c r="C12" s="36" t="inlineStr">
@@ -5792,7 +5797,7 @@
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>Faltan las de Elizabeth, Gabriela y Tonathiu. Cuadradas, mínimo 400×400 px. — RECIBIDAS, pero a 200×200 px. Ver «Pendientes», punto 3.</t>
+          <t>Faltan las de Elizabeth, Gabriela y Tonatiuh. Cuadradas, mínimo 400×400 px. — RECIBIDAS, pero a 200×200 px. Ver «Pendientes», punto 3.</t>
         </is>
       </c>
     </row>
@@ -7126,6 +7131,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="56" t="inlineStr">
         <is>
@@ -7205,6 +7211,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="62" customHeight="1" s="50">
       <c r="A14" s="58" t="inlineStr">
         <is>
@@ -7406,12 +7413,12 @@
     <row r="6" ht="107.25" customHeight="1" s="50">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>tonathiu-munoz</t>
+          <t>tonatiuh-munoz</t>
         </is>
       </c>
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>Tonathiu Muñoz</t>
+          <t>Tonatiuh Muñoz</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -7421,13 +7428,13 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>Tonathiu se define como un ser en constante búsqueda de respuestas, crecimiento y sanación. A lo largo de su camino ha encontrado diversas técnicas, herramientas y conocimientos que le han ayudado a comprenderse mejor y a transformar aspectos importantes de su vida.
+          <t>Tonatiuh se define como un ser en constante búsqueda de respuestas, crecimiento y sanación. A lo largo de su camino ha encontrado diversas técnicas, herramientas y conocimientos que le han ayudado a comprenderse mejor y a transformar aspectos importantes de su vida.
 Hoy comparte estas experiencias y aprendizajes con el propósito de acompañar a otras personas en sus propios procesos, ofreciendo un espacio de escucha, equilibrio y reconexión con sí mismas. Su intención es apoyar a quienes buscan bienestar, claridad y una relación más profunda con su esencia.</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>tonathiu-munoz.jpg</t>
+          <t>tonatiuh-munoz.jpg</t>
         </is>
       </c>
       <c r="F6" s="29" t="n">
@@ -10261,7 +10268,7 @@
       </c>
       <c r="L7" s="32" t="inlineStr">
         <is>
-          <t>tonathiu-munoz</t>
+          <t>tonatiuh-munoz</t>
         </is>
       </c>
       <c r="M7" s="32" t="inlineStr">
@@ -10330,7 +10337,7 @@
       </c>
       <c r="L8" s="32" t="inlineStr">
         <is>
-          <t>tonathiu-munoz</t>
+          <t>tonatiuh-munoz</t>
         </is>
       </c>
       <c r="M8" s="32" t="inlineStr">
@@ -10400,7 +10407,7 @@
       </c>
       <c r="L9" s="32" t="inlineStr">
         <is>
-          <t>tonathiu-munoz</t>
+          <t>tonatiuh-munoz</t>
         </is>
       </c>
       <c r="M9" s="32" t="inlineStr">
@@ -10469,7 +10476,7 @@
       </c>
       <c r="L10" s="32" t="inlineStr">
         <is>
-          <t>tonathiu-munoz</t>
+          <t>tonatiuh-munoz</t>
         </is>
       </c>
       <c r="M10" s="32" t="inlineStr">
@@ -10538,7 +10545,7 @@
       </c>
       <c r="L11" s="32" t="inlineStr">
         <is>
-          <t>tonathiu-munoz</t>
+          <t>tonatiuh-munoz</t>
         </is>
       </c>
       <c r="M11" s="32" t="inlineStr">
